--- a/data/trans_orig/POLIPATOLOGIA_Lim_2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/POLIPATOLOGIA_Lim_2-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dos o más enfermedades crónicas de las que al menos una es limitante en 2012</t>
+          <t>Población con dos o más enfermedades crónicas de las que al menos una es limitante en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>999</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10932</t>
+          <t>9951</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9912</t>
+          <t>10074</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25249</t>
+          <t>26440</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13008</t>
+          <t>12097</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31054</t>
+          <t>30268</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>443214</t>
+          <t>444195</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>453161</t>
+          <t>453147</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>404981</t>
+          <t>403790</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>420318</t>
+          <t>420156</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>853322</t>
+          <t>854108</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>871368</t>
+          <t>872279</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,63%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16386</t>
+          <t>15568</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37543</t>
+          <t>36543</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30992</t>
+          <t>31179</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57669</t>
+          <t>57310</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>53419</t>
+          <t>51290</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>85411</t>
+          <t>84971</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,55%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>649544</t>
+          <t>650544</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>670701</t>
+          <t>671519</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>552586</t>
+          <t>552945</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>579263</t>
+          <t>579076</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1211931</t>
+          <t>1212371</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1243923</t>
+          <t>1246052</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>96,05%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26604</t>
+          <t>26437</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53069</t>
+          <t>52692</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>93352</t>
+          <t>92158</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>134151</t>
+          <t>133393</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>126437</t>
+          <t>128686</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>173612</t>
+          <t>175463</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,6%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>628794</t>
+          <t>629171</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>655259</t>
+          <t>655426</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>576699</t>
+          <t>577457</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>617498</t>
+          <t>618692</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1219100</t>
+          <t>1217249</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1266275</t>
+          <t>1264026</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>90,76%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64128</t>
+          <t>63080</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>100020</t>
+          <t>100281</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>119293</t>
+          <t>118137</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>162160</t>
+          <t>161812</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>194174</t>
+          <t>193921</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>247645</t>
+          <t>251590</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,44%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>514597</t>
+          <t>514336</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>550489</t>
+          <t>551537</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>454039</t>
+          <t>454387</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>496906</t>
+          <t>498062</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>983171</t>
+          <t>979226</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1036642</t>
+          <t>1036895</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>84,24%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>92913</t>
+          <t>94376</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>130705</t>
+          <t>129789</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>181066</t>
+          <t>181280</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>225396</t>
+          <t>225576</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>50,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>284567</t>
+          <t>286557</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>343545</t>
+          <t>344528</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>39,27%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>298724</t>
+          <t>299640</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>336516</t>
+          <t>335053</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>222404</t>
+          <t>222224</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>266734</t>
+          <t>266520</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>49,67%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>533684</t>
+          <t>532701</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>592662</t>
+          <t>590672</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>67,33%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>137820</t>
+          <t>139506</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>176977</t>
+          <t>176732</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>57,13%</t>
+          <t>57,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>199756</t>
+          <t>200682</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>237037</t>
+          <t>237863</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>56,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>67,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>352552</t>
+          <t>350502</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>403940</t>
+          <t>402123</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>53,11%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>60,58%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>132809</t>
+          <t>133054</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>171966</t>
+          <t>170280</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>116959</t>
+          <t>116133</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>154240</t>
+          <t>153314</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>259842</t>
+          <t>261659</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>311230</t>
+          <t>313280</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>47,2%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>149601</t>
+          <t>149306</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>181396</t>
+          <t>181906</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>72,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>287320</t>
+          <t>288533</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>321830</t>
+          <t>322052</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>74,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>447978</t>
+          <t>448153</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>494957</t>
+          <t>493499</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,25%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>68455</t>
+          <t>67945</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>100250</t>
+          <t>100545</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>67149</t>
+          <t>66927</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>101659</t>
+          <t>100446</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>143873</t>
+          <t>145331</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>190852</t>
+          <t>190677</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,85%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>539147</t>
+          <t>538765</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>628616</t>
+          <t>628083</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>985463</t>
+          <t>990630</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1095935</t>
+          <t>1099426</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1547932</t>
+          <t>1554153</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1698386</t>
+          <t>1693328</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,24%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2798163</t>
+          <t>2798696</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2887632</t>
+          <t>2888014</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2462374</t>
+          <t>2458883</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2572846</t>
+          <t>2567679</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5286702</t>
+          <t>5291760</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5437156</t>
+          <t>5430935</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>77,75%</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dos o más enfermedades crónicas de las que al menos una es limitante en 2016</t>
+          <t>Población con dos o más enfermedades crónicas de las que al menos una es limitante en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2417</t>
+          <t>2815</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12901</t>
+          <t>13413</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17640</t>
+          <t>16046</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36239</t>
+          <t>35451</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21621</t>
+          <t>20743</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44750</t>
+          <t>42875</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>406562</t>
+          <t>406050</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>417046</t>
+          <t>416648</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>359516</t>
+          <t>360304</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>378115</t>
+          <t>379709</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>770468</t>
+          <t>772343</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>793597</t>
+          <t>794475</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,46%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10672</t>
+          <t>10861</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29544</t>
+          <t>31056</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25294</t>
+          <t>25706</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48382</t>
+          <t>48438</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>40280</t>
+          <t>41457</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>69045</t>
+          <t>72281</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>560952</t>
+          <t>559440</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>579824</t>
+          <t>579635</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>515162</t>
+          <t>515106</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>538250</t>
+          <t>537838</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1084995</t>
+          <t>1081759</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1113760</t>
+          <t>1112583</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,41%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26675</t>
+          <t>25584</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50559</t>
+          <t>50861</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>52718</t>
+          <t>52855</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>83859</t>
+          <t>83390</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>86284</t>
+          <t>86147</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>127277</t>
+          <t>125235</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,41%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>618538</t>
+          <t>618236</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>642422</t>
+          <t>643513</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>577527</t>
+          <t>577996</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>608668</t>
+          <t>608531</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1203206</t>
+          <t>1205248</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1244199</t>
+          <t>1244336</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,53%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73150</t>
+          <t>73199</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>107612</t>
+          <t>111817</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>120517</t>
+          <t>118839</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>162506</t>
+          <t>160782</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>204461</t>
+          <t>204302</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>262685</t>
+          <t>262926</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,3%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>538436</t>
+          <t>534231</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>572898</t>
+          <t>572849</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>486571</t>
+          <t>488295</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>528560</t>
+          <t>530238</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1032440</t>
+          <t>1032199</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1090664</t>
+          <t>1090823</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>79,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,23%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>93556</t>
+          <t>93189</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>132861</t>
+          <t>133750</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>169655</t>
+          <t>170108</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>215604</t>
+          <t>213884</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>272777</t>
+          <t>273333</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>334804</t>
+          <t>335293</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,4%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>345057</t>
+          <t>344168</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>384362</t>
+          <t>384729</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>281245</t>
+          <t>282965</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>327194</t>
+          <t>326741</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>56,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>639963</t>
+          <t>639474</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>701990</t>
+          <t>701434</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>71,96%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>95605</t>
+          <t>96296</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>130196</t>
+          <t>129062</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>180685</t>
+          <t>180347</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>219556</t>
+          <t>219378</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>47,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>58,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>284280</t>
+          <t>287177</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>340016</t>
+          <t>340957</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>47,88%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>204134</t>
+          <t>205268</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>238725</t>
+          <t>238034</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>61,06%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>71,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>158206</t>
+          <t>158384</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>197077</t>
+          <t>197415</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>372076</t>
+          <t>371135</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>427812</t>
+          <t>424915</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>52,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>60,08%</t>
+          <t>59,67%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>114879</t>
+          <t>117604</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>144990</t>
+          <t>146183</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>56,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>228287</t>
+          <t>227645</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>272937</t>
+          <t>273070</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>57,05%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>68,21%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>354210</t>
+          <t>355518</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>410734</t>
+          <t>407141</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>61,95%</t>
         </is>
       </c>
     </row>
@@ -5882,12 +5882,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>112008</t>
+          <t>110815</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>142119</t>
+          <t>139394</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>54,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>127232</t>
+          <t>127099</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>171882</t>
+          <t>172524</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>246433</t>
+          <t>250026</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>302957</t>
+          <t>301649</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>45,9%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>465684</t>
+          <t>464515</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>548403</t>
+          <t>548687</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>858554</t>
+          <t>860858</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>967781</t>
+          <t>968200</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1346697</t>
+          <t>1344647</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1488780</t>
+          <t>1484176</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,39%</t>
         </is>
       </c>
     </row>
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2845947</t>
+          <t>2845663</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2928666</t>
+          <t>2929835</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2576761</t>
+          <t>2576342</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2685988</t>
+          <t>2683684</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5450112</t>
+          <t>5454716</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5592195</t>
+          <t>5594245</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>80,62%</t>
         </is>
       </c>
     </row>
@@ -6495,7 +6495,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dos o más enfermedades crónicas de las que al menos una es limitante en 2023</t>
+          <t>Población con dos o más enfermedades crónicas de las que al menos una es limitante en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6690,12 +6690,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7527</t>
+          <t>7420</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39809</t>
+          <t>38070</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27478</t>
+          <t>27957</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>63260</t>
+          <t>62984</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6760,12 +6760,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>42224</t>
+          <t>41023</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>90584</t>
+          <t>86752</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,16%</t>
         </is>
       </c>
     </row>
@@ -6803,12 +6803,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>360178</t>
+          <t>361917</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>392460</t>
+          <t>392567</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6818,12 +6818,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6838,12 +6838,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>249940</t>
+          <t>250216</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>285722</t>
+          <t>285243</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6853,12 +6853,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6873,12 +6873,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>622603</t>
+          <t>626435</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>670963</t>
+          <t>672164</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,25%</t>
         </is>
       </c>
     </row>
@@ -7033,12 +7033,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15483</t>
+          <t>16460</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39858</t>
+          <t>39328</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7048,82 +7048,82 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>9,29%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>62879</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>39545</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>82511</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>12,28%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>7,72%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>16,11%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>88056</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>65242</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>111331</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
           <t>9,41%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>62879</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>37325</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>81891</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>12,28%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>7,29%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>15,99%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>88056</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>63549</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>112829</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>9,41%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,9%</t>
         </is>
       </c>
     </row>
@@ -7146,12 +7146,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>383689</t>
+          <t>384219</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>408064</t>
+          <t>407087</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7161,82 +7161,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>90,71%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,11%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>449214</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>429582</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>472548</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>87,72%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>83,89%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>92,28%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>683</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>847584</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>824309</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>870398</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
           <t>90,59%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,34%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>401</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>449214</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>430202</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>474768</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>87,72%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>84,01%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>92,71%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>683</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>847584</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>822811</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>872091</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>90,59%</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,03%</t>
         </is>
       </c>
     </row>
@@ -7376,12 +7376,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35023</t>
+          <t>34564</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61325</t>
+          <t>61076</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7391,12 +7391,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7411,12 +7411,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>76262</t>
+          <t>73055</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>116659</t>
+          <t>116476</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7426,12 +7426,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7446,12 +7446,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>121504</t>
+          <t>123438</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>168957</t>
+          <t>170589</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,12%</t>
         </is>
       </c>
     </row>
@@ -7489,12 +7489,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>475013</t>
+          <t>475262</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>501315</t>
+          <t>501774</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>475343</t>
+          <t>475526</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>515740</t>
+          <t>518947</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7559,12 +7559,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>959383</t>
+          <t>957751</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1006836</t>
+          <t>1004902</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,06%</t>
         </is>
       </c>
     </row>
@@ -7719,12 +7719,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52041</t>
+          <t>52966</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>177585</t>
+          <t>178638</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7734,12 +7734,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7754,12 +7754,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>167224</t>
+          <t>166594</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>219673</t>
+          <t>218356</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7769,12 +7769,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7789,12 +7789,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>185812</t>
+          <t>198839</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>389991</t>
+          <t>391581</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7804,12 +7804,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,46%</t>
         </is>
       </c>
     </row>
@@ -7832,12 +7832,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>710201</t>
+          <t>709148</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>835745</t>
+          <t>834820</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7847,12 +7847,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>493208</t>
+          <t>494525</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>545657</t>
+          <t>546287</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7882,12 +7882,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7902,12 +7902,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1210676</t>
+          <t>1209086</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1414855</t>
+          <t>1401828</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7917,12 +7917,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>87,58%</t>
         </is>
       </c>
     </row>
@@ -8062,12 +8062,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>134070</t>
+          <t>136141</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>172938</t>
+          <t>175927</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8077,12 +8077,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>197931</t>
+          <t>198350</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>231971</t>
+          <t>233105</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8112,12 +8112,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>342346</t>
+          <t>342344</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>388296</t>
+          <t>385307</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>427164</t>
+          <t>425093</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8190,12 +8190,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>68,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>315934</t>
+          <t>314800</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>349974</t>
+          <t>349555</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8225,12 +8225,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>57,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8250,7 +8250,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>766793</t>
+          <t>766795</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>92204</t>
+          <t>93375</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>119345</t>
+          <t>120039</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8420,12 +8420,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>77961</t>
+          <t>85594</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>292506</t>
+          <t>292210</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8455,12 +8455,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8475,12 +8475,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>162040</t>
+          <t>159397</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>381159</t>
+          <t>380885</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8490,12 +8490,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>39,0%</t>
         </is>
       </c>
     </row>
@@ -8518,12 +8518,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>248820</t>
+          <t>248126</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>275961</t>
+          <t>274790</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8533,12 +8533,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>315862</t>
+          <t>316158</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>530407</t>
+          <t>522774</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8588,12 +8588,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>595374</t>
+          <t>595648</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>814493</t>
+          <t>817136</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8603,12 +8603,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>83,68%</t>
         </is>
       </c>
     </row>
@@ -8748,12 +8748,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>109979</t>
+          <t>110376</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>136131</t>
+          <t>136637</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8763,12 +8763,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>279126</t>
+          <t>278235</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>304972</t>
+          <t>306282</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8798,12 +8798,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>65,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8818,12 +8818,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>395421</t>
+          <t>396508</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>436265</t>
+          <t>435466</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8833,12 +8833,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>61,46%</t>
         </is>
       </c>
     </row>
@@ -8861,12 +8861,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>146628</t>
+          <t>146122</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>172780</t>
+          <t>172383</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8876,12 +8876,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>51,68%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>60,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>120859</t>
+          <t>119549</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>146705</t>
+          <t>147596</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8911,12 +8911,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8931,12 +8931,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>272325</t>
+          <t>273124</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>313169</t>
+          <t>312082</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8946,12 +8946,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>44,04%</t>
         </is>
       </c>
     </row>
@@ -9091,12 +9091,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>470623</t>
+          <t>457566</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>656562</t>
+          <t>659443</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9126,12 +9126,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>895754</t>
+          <t>872848</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1194646</t>
+          <t>1194874</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9141,12 +9141,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9161,12 +9161,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1456828</t>
+          <t>1444766</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1814962</t>
+          <t>1814112</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9176,12 +9176,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,29%</t>
         </is>
       </c>
     </row>
@@ -9204,12 +9204,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2803255</t>
+          <t>2800374</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2989194</t>
+          <t>3002251</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9239,12 +9239,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2517634</t>
+          <t>2517406</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2816526</t>
+          <t>2839432</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9254,12 +9254,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9274,12 +9274,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5357135</t>
+          <t>5357985</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5715269</t>
+          <t>5727331</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9289,12 +9289,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>79,86%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/POLIPATOLOGIA_Lim_2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/POLIPATOLOGIA_Lim_2-Edad-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>984</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9951</t>
+          <t>9879</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10074</t>
+          <t>9554</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26440</t>
+          <t>26186</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12097</t>
+          <t>12151</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30268</t>
+          <t>29709</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>444195</t>
+          <t>444267</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>453147</t>
+          <t>453162</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>403790</t>
+          <t>404044</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>420156</t>
+          <t>420676</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>854108</t>
+          <t>854667</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>872279</t>
+          <t>872225</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15568</t>
+          <t>16061</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36543</t>
+          <t>36333</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31179</t>
+          <t>30376</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57310</t>
+          <t>56731</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>51290</t>
+          <t>54126</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>84971</t>
+          <t>86239</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>650544</t>
+          <t>650754</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>671519</t>
+          <t>671026</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>552945</t>
+          <t>553524</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>579076</t>
+          <t>579879</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1212371</t>
+          <t>1211103</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1246052</t>
+          <t>1243216</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,83%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26437</t>
+          <t>25795</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52692</t>
+          <t>52071</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>92158</t>
+          <t>91709</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>133393</t>
+          <t>132148</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>128686</t>
+          <t>126619</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>175463</t>
+          <t>175605</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,61%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>629171</t>
+          <t>629792</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>655426</t>
+          <t>656068</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>577457</t>
+          <t>578702</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>618692</t>
+          <t>619141</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1217249</t>
+          <t>1217107</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1264026</t>
+          <t>1266093</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,91%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>63080</t>
+          <t>63699</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>100281</t>
+          <t>97694</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>118137</t>
+          <t>119941</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>161812</t>
+          <t>162733</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>193921</t>
+          <t>192594</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>251590</t>
+          <t>249371</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,26%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>514336</t>
+          <t>516923</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>551537</t>
+          <t>550918</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>454387</t>
+          <t>453466</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>498062</t>
+          <t>496258</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>979226</t>
+          <t>981445</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1036895</t>
+          <t>1038222</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,35%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>94376</t>
+          <t>93282</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>129789</t>
+          <t>130611</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>181280</t>
+          <t>182399</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>225576</t>
+          <t>227061</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>50,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>286557</t>
+          <t>288720</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>344528</t>
+          <t>344565</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>39,28%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>299640</t>
+          <t>298818</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>335053</t>
+          <t>336147</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>78,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>222224</t>
+          <t>220739</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>266520</t>
+          <t>265401</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>49,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>59,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>532701</t>
+          <t>532664</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>590672</t>
+          <t>588509</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>60,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>67,09%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>139506</t>
+          <t>139209</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>176732</t>
+          <t>175707</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>57,05%</t>
+          <t>56,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>200682</t>
+          <t>199377</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>237863</t>
+          <t>238754</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>56,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>350502</t>
+          <t>352763</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>402123</t>
+          <t>404969</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>60,58%</t>
+          <t>61,01%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>133054</t>
+          <t>134079</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>170280</t>
+          <t>170577</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>55,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>116133</t>
+          <t>115242</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>153314</t>
+          <t>154619</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>261659</t>
+          <t>258813</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>313280</t>
+          <t>311019</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>46,86%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>149306</t>
+          <t>149693</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>181906</t>
+          <t>180139</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>59,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>72,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>288533</t>
+          <t>286948</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>322052</t>
+          <t>322006</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>448153</t>
+          <t>445658</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>493499</t>
+          <t>493028</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>77,18%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>67945</t>
+          <t>69712</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>100545</t>
+          <t>100158</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>66927</t>
+          <t>66973</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>100446</t>
+          <t>102031</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>145331</t>
+          <t>145802</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>190677</t>
+          <t>193172</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>30,24%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>538765</t>
+          <t>536420</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>628083</t>
+          <t>633209</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>990630</t>
+          <t>987012</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1099426</t>
+          <t>1089080</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1554153</t>
+          <t>1545276</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1693328</t>
+          <t>1696504</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,29%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2798696</t>
+          <t>2793570</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2888014</t>
+          <t>2890359</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2458883</t>
+          <t>2469229</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2567679</t>
+          <t>2571297</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5291760</t>
+          <t>5288584</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5430935</t>
+          <t>5439812</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>77,88%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2815</t>
+          <t>2478</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13413</t>
+          <t>13259</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16046</t>
+          <t>16279</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35451</t>
+          <t>35011</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20743</t>
+          <t>21928</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42875</t>
+          <t>43121</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>406050</t>
+          <t>406204</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>416648</t>
+          <t>416985</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>360304</t>
+          <t>360744</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>379709</t>
+          <t>379476</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>772343</t>
+          <t>772097</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>794475</t>
+          <t>793290</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,31%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10861</t>
+          <t>10636</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31056</t>
+          <t>28361</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25706</t>
+          <t>25902</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48438</t>
+          <t>49422</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>41457</t>
+          <t>40922</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>72281</t>
+          <t>70727</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>559440</t>
+          <t>562135</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>579635</t>
+          <t>579860</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>515106</t>
+          <t>514122</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>537838</t>
+          <t>537642</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1081759</t>
+          <t>1083313</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1112583</t>
+          <t>1113118</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,45%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25584</t>
+          <t>25666</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50861</t>
+          <t>50859</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>52855</t>
+          <t>53077</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>83390</t>
+          <t>85453</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>86147</t>
+          <t>87909</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>125235</t>
+          <t>127709</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,6%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>618236</t>
+          <t>618238</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>643513</t>
+          <t>643431</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>577996</t>
+          <t>575933</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>608531</t>
+          <t>608309</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1205248</t>
+          <t>1202774</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1244336</t>
+          <t>1242574</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,39%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73199</t>
+          <t>73476</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>111817</t>
+          <t>108499</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>118839</t>
+          <t>120200</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>160782</t>
+          <t>162106</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>204302</t>
+          <t>203875</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>262926</t>
+          <t>260370</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,1%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>534231</t>
+          <t>537549</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>572849</t>
+          <t>572572</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>488295</t>
+          <t>486971</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>530238</t>
+          <t>528877</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>81,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1032199</t>
+          <t>1034755</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1090823</t>
+          <t>1091250</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>84,26%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>93189</t>
+          <t>93604</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>133750</t>
+          <t>132912</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>170108</t>
+          <t>169070</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>213884</t>
+          <t>214803</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>273333</t>
+          <t>271317</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>335293</t>
+          <t>334332</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,3%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>344168</t>
+          <t>345006</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>384729</t>
+          <t>384314</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>72,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>282965</t>
+          <t>282046</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>326741</t>
+          <t>327779</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>56,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>639474</t>
+          <t>640435</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>701434</t>
+          <t>703450</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>65,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>72,17%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>96296</t>
+          <t>95045</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>129062</t>
+          <t>130628</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>180347</t>
+          <t>179726</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>219378</t>
+          <t>219350</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>47,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>287177</t>
+          <t>285960</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>340957</t>
+          <t>337994</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>47,46%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>205268</t>
+          <t>203702</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>238034</t>
+          <t>239285</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>61,4%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>71,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>158384</t>
+          <t>158412</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>197415</t>
+          <t>198036</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>52,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>371135</t>
+          <t>374098</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>424915</t>
+          <t>426132</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>52,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>59,67%</t>
+          <t>59,84%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>117604</t>
+          <t>117048</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>146183</t>
+          <t>145469</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>56,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>227645</t>
+          <t>232101</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>273070</t>
+          <t>274862</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>56,89%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>68,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>355518</t>
+          <t>355903</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>407141</t>
+          <t>409800</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>54,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>62,36%</t>
         </is>
       </c>
     </row>
@@ -5882,12 +5882,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>110815</t>
+          <t>111529</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>139394</t>
+          <t>139950</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>54,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>127099</t>
+          <t>125307</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>172524</t>
+          <t>168068</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>250026</t>
+          <t>247367</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>301649</t>
+          <t>301264</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>45,84%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>464515</t>
+          <t>465378</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>548687</t>
+          <t>550763</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>860858</t>
+          <t>858479</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>968200</t>
+          <t>975038</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1344647</t>
+          <t>1352608</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1484176</t>
+          <t>1490115</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,47%</t>
         </is>
       </c>
     </row>
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2845663</t>
+          <t>2843587</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2929835</t>
+          <t>2928972</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2576342</t>
+          <t>2569504</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2683684</t>
+          <t>2686063</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5454716</t>
+          <t>5448777</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5594245</t>
+          <t>5586284</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>80,51%</t>
         </is>
       </c>
     </row>
@@ -6685,32 +6685,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>18464</t>
+          <t>17890</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7420</t>
+          <t>6825</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38070</t>
+          <t>36268</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6720,32 +6720,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>42979</t>
+          <t>52649</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27957</t>
+          <t>35432</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>62984</t>
+          <t>75278</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6755,32 +6755,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>61443</t>
+          <t>70538</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41023</t>
+          <t>48674</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>86752</t>
+          <t>96691</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,55%</t>
         </is>
       </c>
     </row>
@@ -6798,32 +6798,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>381523</t>
+          <t>389903</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>361917</t>
+          <t>371525</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>392567</t>
+          <t>400968</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6833,32 +6833,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>270221</t>
+          <t>309863</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>250216</t>
+          <t>287234</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>285243</t>
+          <t>327080</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6868,32 +6868,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>651744</t>
+          <t>699767</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>626435</t>
+          <t>673614</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>672164</t>
+          <t>721631</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>93,68%</t>
         </is>
       </c>
     </row>
@@ -6911,17 +6911,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6946,17 +6946,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6981,17 +6981,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7028,32 +7028,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>25178</t>
+          <t>28212</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16460</t>
+          <t>17445</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39328</t>
+          <t>41687</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7063,32 +7063,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>62879</t>
+          <t>67253</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39545</t>
+          <t>51177</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>82511</t>
+          <t>84619</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7098,32 +7098,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>88056</t>
+          <t>95465</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>65242</t>
+          <t>77542</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>111331</t>
+          <t>118786</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,14%</t>
         </is>
       </c>
     </row>
@@ -7141,32 +7141,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>398369</t>
+          <t>448678</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>384219</t>
+          <t>435203</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>407087</t>
+          <t>459445</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7176,32 +7176,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>449214</t>
+          <t>434480</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>429582</t>
+          <t>417114</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>472548</t>
+          <t>450556</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7211,32 +7211,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>847584</t>
+          <t>883158</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>824309</t>
+          <t>859837</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>870398</t>
+          <t>901081</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>92,08%</t>
         </is>
       </c>
     </row>
@@ -7254,17 +7254,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7289,17 +7289,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7324,17 +7324,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7371,32 +7371,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>47150</t>
+          <t>51557</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34564</t>
+          <t>37649</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61076</t>
+          <t>68395</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7406,32 +7406,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>99236</t>
+          <t>115942</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>73055</t>
+          <t>100066</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>116476</t>
+          <t>134420</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7441,32 +7441,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>146386</t>
+          <t>167498</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>123438</t>
+          <t>147837</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>170589</t>
+          <t>192150</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,45%</t>
         </is>
       </c>
     </row>
@@ -7484,32 +7484,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>489188</t>
+          <t>569280</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>475262</t>
+          <t>552442</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>501774</t>
+          <t>583188</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7519,32 +7519,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>492766</t>
+          <t>507251</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>475526</t>
+          <t>488773</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>518947</t>
+          <t>523127</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>78,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7554,32 +7554,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>981954</t>
+          <t>1076531</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>957751</t>
+          <t>1051879</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1004902</t>
+          <t>1096192</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>88,12%</t>
         </is>
       </c>
     </row>
@@ -7597,17 +7597,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7632,17 +7632,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7667,17 +7667,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7714,32 +7714,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>122500</t>
+          <t>130316</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52966</t>
+          <t>110651</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>178638</t>
+          <t>154673</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7749,32 +7749,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>197741</t>
+          <t>210665</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>166594</t>
+          <t>190666</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>218356</t>
+          <t>228789</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7784,32 +7784,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>320241</t>
+          <t>340981</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>198839</t>
+          <t>311915</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>391581</t>
+          <t>368613</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>25,64%</t>
         </is>
       </c>
     </row>
@@ -7827,32 +7827,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>765286</t>
+          <t>570301</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>709148</t>
+          <t>545944</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>834820</t>
+          <t>589966</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7862,32 +7862,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>515140</t>
+          <t>526221</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>494525</t>
+          <t>508097</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>546287</t>
+          <t>546220</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>71,41%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7897,32 +7897,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1280426</t>
+          <t>1096523</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1209086</t>
+          <t>1068891</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1401828</t>
+          <t>1125589</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>74,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>78,3%</t>
         </is>
       </c>
     </row>
@@ -7940,17 +7940,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7975,17 +7975,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8010,17 +8010,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8057,32 +8057,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>153379</t>
+          <t>163648</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>136141</t>
+          <t>144744</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>175927</t>
+          <t>186272</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8092,32 +8092,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>215231</t>
+          <t>238289</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>198350</t>
+          <t>219495</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>233105</t>
+          <t>255993</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>42,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8127,32 +8127,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>368610</t>
+          <t>401936</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>342344</t>
+          <t>375115</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>395814</t>
+          <t>429954</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>35,29%</t>
         </is>
       </c>
     </row>
@@ -8170,32 +8170,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>407855</t>
+          <t>445698</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>385307</t>
+          <t>423074</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>425093</t>
+          <t>464602</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>73,14%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>69,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8205,32 +8205,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>332674</t>
+          <t>370566</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>314800</t>
+          <t>352862</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>349555</t>
+          <t>389360</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>60,72%</t>
+          <t>60,86%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>57,46%</t>
+          <t>57,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8240,32 +8240,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>740529</t>
+          <t>816266</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>713325</t>
+          <t>788248</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>766795</t>
+          <t>843087</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>69,21%</t>
         </is>
       </c>
     </row>
@@ -8283,17 +8283,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8318,17 +8318,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8353,17 +8353,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8400,32 +8400,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>105434</t>
+          <t>114318</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>93375</t>
+          <t>98944</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>120039</t>
+          <t>129552</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8435,32 +8435,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>188816</t>
+          <t>205740</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>85594</t>
+          <t>191141</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>292210</t>
+          <t>221635</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>50,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8470,32 +8470,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>294250</t>
+          <t>320059</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>159397</t>
+          <t>297855</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>380885</t>
+          <t>341103</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>40,31%</t>
         </is>
       </c>
     </row>
@@ -8513,32 +8513,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>262731</t>
+          <t>292762</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>248126</t>
+          <t>277528</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>274790</t>
+          <t>308136</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>68,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8548,32 +8548,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>419552</t>
+          <t>233426</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>316158</t>
+          <t>217531</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>522774</t>
+          <t>248025</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>53,15%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8583,32 +8583,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>682283</t>
+          <t>526187</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>595648</t>
+          <t>505143</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>817136</t>
+          <t>548391</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>62,18%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>59,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>64,8%</t>
         </is>
       </c>
     </row>
@@ -8626,17 +8626,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8696,17 +8696,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8743,32 +8743,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>122991</t>
+          <t>135051</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>110376</t>
+          <t>119700</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>136637</t>
+          <t>149097</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8778,32 +8778,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>292721</t>
+          <t>318877</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>278235</t>
+          <t>301710</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>306282</t>
+          <t>333380</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>68,63%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>65,34%</t>
+          <t>64,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8813,32 +8813,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>415712</t>
+          <t>453929</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>396508</t>
+          <t>433110</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>435466</t>
+          <t>475538</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,38%</t>
         </is>
       </c>
     </row>
@@ -8856,32 +8856,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>159768</t>
+          <t>175147</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>146122</t>
+          <t>161101</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>172383</t>
+          <t>190498</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>51,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>61,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8891,32 +8891,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>133110</t>
+          <t>145732</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>119549</t>
+          <t>131229</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>147596</t>
+          <t>162899</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8926,32 +8926,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>292878</t>
+          <t>320878</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>273124</t>
+          <t>299269</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>312082</t>
+          <t>341697</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>44,1%</t>
         </is>
       </c>
     </row>
@@ -8969,17 +8969,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9004,17 +9004,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9039,17 +9039,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9086,32 +9086,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>595095</t>
+          <t>640992</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>457566</t>
+          <t>597395</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>659443</t>
+          <t>691624</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9121,32 +9121,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1099603</t>
+          <t>1209415</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>872848</t>
+          <t>1167141</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1194874</t>
+          <t>1265328</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9156,32 +9156,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1694698</t>
+          <t>1850407</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1444766</t>
+          <t>1775947</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1814112</t>
+          <t>1927855</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>26,52%</t>
         </is>
       </c>
     </row>
@@ -9199,32 +9199,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2864722</t>
+          <t>2891770</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2800374</t>
+          <t>2841138</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3002251</t>
+          <t>2935367</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9234,32 +9234,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2612677</t>
+          <t>2527539</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2517406</t>
+          <t>2471626</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2839432</t>
+          <t>2569813</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>66,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>68,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9269,32 +9269,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>5477399</t>
+          <t>5419309</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5357985</t>
+          <t>5341861</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5727331</t>
+          <t>5493769</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>75,57%</t>
         </is>
       </c>
     </row>
@@ -9312,17 +9312,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9347,17 +9347,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9382,17 +9382,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
